--- a/data/trans_dic/IP31B_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31B_R_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,23; 37,39</t>
+          <t>21,16; 35,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,61; 43,54</t>
+          <t>22,98; 38,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,45; 38,29</t>
+          <t>24,12; 33,61</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,26; 42,61</t>
+          <t>27,45; 39,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,47; 41,7</t>
+          <t>25,23; 37,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,64; 39,97</t>
+          <t>27,9; 36,39</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>36,98%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,23; 65,48</t>
+          <t>32,08; 46,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,51; 47,86</t>
+          <t>28,46; 42,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,78; 56,24</t>
+          <t>32,15; 42,51</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,79; 31,31</t>
+          <t>25,62; 36,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,44; 37,4</t>
+          <t>18,85; 29,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,45; 33,11</t>
+          <t>23,96; 32,08</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>29,68; 43,52</t>
+          <t>29,95; 36,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,59; 39,0</t>
+          <t>26,9; 33,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,73; 39,02</t>
+          <t>29,32; 34,05</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34506</t>
+          <t>33771</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42717</t>
+          <t>35107</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77224</t>
+          <t>68878</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27678; 42719</t>
+          <t>25459; 43206</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31400; 57911</t>
+          <t>27252; 45173</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62937; 94676</t>
+          <t>57617; 80283</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>90</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>64429</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87602</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152031</t>
+          <t>131816</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52378; 78977</t>
+          <t>63468; 92179</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72943; 103204</t>
+          <t>45385; 66876</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132630; 172996</t>
+          <t>114728; 149621</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78853</t>
+          <t>64936</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73836</t>
+          <t>53222</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152690</t>
+          <t>118158</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56290; 121924</t>
+          <t>53326; 77880</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61221; 87434</t>
+          <t>43625; 65770</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>128306; 207465</t>
+          <t>102707; 135811</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54993</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96932</t>
+          <t>90810</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>32342; 51174</t>
+          <t>42327; 60955</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44864; 65948</t>
+          <t>30683; 48022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83090; 112513</t>
+          <t>78598; 105235</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>289</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>219727</t>
+          <t>225858</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>259149</t>
+          <t>183803</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>478876</t>
+          <t>409662</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>192703; 282508</t>
+          <t>204522; 250878</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>233608; 288414</t>
+          <t>165303; 203868</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>440688; 541957</t>
+          <t>380431; 441822</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31B_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31B_R_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>28,07%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>21,16; 35,91</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>22,98; 38,09</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24,12; 33,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>32,63%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>27,45; 39,86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>25,23; 37,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>27,9; 36,39</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>39,07%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>34,72%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>36,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>32,08; 46,85</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28,46; 42,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>32,15; 42,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>31,3%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>25,62; 36,89</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>18,85; 29,5</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23,96; 32,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>29,91%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>31,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>29,95; 36,73</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26,9; 33,17</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29,32; 34,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2807139460756999</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.2960174589304434</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2883110814162829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>33771</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>35107</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68878</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.2116232029764605</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.2297888270836692</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.2411763532689559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>25459; 43206</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>27252; 45173</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57617; 80283</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3591450273480141</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3808939984443101</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.336052191740237</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3262536161668729</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.3133311863849574</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.3205989691625434</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>75443</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>56373</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>131816</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.2744668668229543</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.2522559425399465</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.2790374286402036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>63468; 92179</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>45385; 66876</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>114728; 149621</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.3986283666348023</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.3717113156368347</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.3639022096409237</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3906582437602416</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3472344302820917</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3698264234049329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>64936</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>53222</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>118158</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.3208080731642572</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.2846261091015965</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3214662838949515</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>53326; 77880</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43625; 65770</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>102707; 135811</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4685261349252145</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4291033477449588</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4250781475861481</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.3129635227376133</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2401963320915556</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.276849509301647</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>51708</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>39102</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>90810</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.2561836648635888</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1884794563724436</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.2396180257031305</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>42327; 60955</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30683; 48022</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>78598; 105235</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.3689317633721402</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2949940423349086</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3208269076664824</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.330691749211116</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.2990732199520793</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.3157160015919697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>225858</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>183803</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>409662</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.2994523635459768</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.2689715252792208</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.2931887174093058</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>204522; 250878</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>165303; 203868</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>380431; 441822</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.3673235895481225</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.3317212280719505</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.3405006069469989</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que se cepillan los dientes una o ninguna vez al día (tasa de respuesta: 99,35%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>33771</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>35107</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>68878</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>25459</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>27252</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>57617</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>43206</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>80283</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>75443</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>56373</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>131816</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>63468</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>45385</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>114728</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>92179</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>66876</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>149621</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>64936</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>53222</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>118158</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>53326</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>43625</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>102707</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>77880</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>65770</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>135811</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>51708</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>39102</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>90810</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>42327</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>30683</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>78598</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>60955</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>48022</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>105235</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>347</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>225858</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>183803</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>409662</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>204522</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>165303</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>380431</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>250878</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>203868</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>441822</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>